--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.197.000</t>
+          <t>Rp2.366.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.248.500</t>
+          <t>Rp15.326.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp6.436.000</t>
+          <t>Rp5.636.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.025.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.752.000</t>
+          <t>Rp4.851.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.377.000</t>
+          <t>Rp1.539.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.750.000</t>
+          <t>Rp16.900.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.896.000</t>
+          <t>Rp2.296.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.040.000</t>
+          <t>Rp7.315.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.366.000</t>
+          <t>Rp5.528.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.825.000</t>
+          <t>Rp17.875.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp8.050.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.400.000</t>
+          <t>Rp12.900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp625.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.043.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.226.000</t>
+          <t>Rp2.326.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>128</v>
       </c>
       <c r="D70" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.533.000</t>
+          <t>Rp3.782.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>96</v>
       </c>
       <c r="D71" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.820.000</t>
+          <t>Rp4.570.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.030.000</t>
+          <t>Rp8.115.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.900.000</t>
+          <t>Rp14.800.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp185.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp825.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp15.140.000</t>
+          <t>Rp15.320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp237.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.485.000</t>
+          <t>Rp3.588.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.599.982</t>
+          <t>Rp3.799.981</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.270.500</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.660.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.695.000</t>
+          <t>Rp6.785.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.295.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.295.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp910.000</t>
+          <t>Rp1.190.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.556.000</t>
+          <t>Rp1.754.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.762.000</t>
+          <t>Rp4.257.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.366.000</t>
+          <t>Rp2.535.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.129.000</t>
+          <t>Rp3.427.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.520.000</t>
+          <t>Rp16.020.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.636.000</t>
+          <t>Rp5.834.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.096.000</t>
+          <t>Rp2.709.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.622.000</t>
+          <t>Rp3.740.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.265.000</t>
+          <t>Rp3.045.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.867.000</t>
+          <t>Rp7.763.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>45</v>
       </c>
       <c r="D47" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.525.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>85</v>
       </c>
       <c r="D61" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp961.000</t>
+          <t>Rp741.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp960.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.030.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp4.570.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.851.000</t>
+          <t>Rp5.148.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.533.000</t>
+          <t>Rp2.682.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.539.000</t>
+          <t>Rp1.701.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.668.000</t>
+          <t>Rp7.002.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.300.000</t>
+          <t>Rp12.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp630.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.920.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.894.000</t>
+          <t>Rp5.294.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.930.000</t>
+          <t>Rp7.425.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.130.000</t>
+          <t>Rp630.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.800.000</t>
+          <t>Rp14.150.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.296.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp555.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>80</v>
       </c>
       <c r="D56" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp593.000</t>
+          <t>Rp716.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp1.940.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp250.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.536.000</t>
+          <t>Rp2.272.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp24.100.000</t>
+          <t>Rp24.350.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.210.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp564.000</t>
+          <t>Rp752.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp16.875.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp14.915.000</t>
+          <t>Rp15.190.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.192.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.750.000</t>
+          <t>Rp17.350.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.528.000</t>
+          <t>Rp5.690.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.230.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.904.000</t>
+          <t>Rp5.058.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.875.000</t>
+          <t>Rp18.525.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.948.000</t>
+          <t>Rp3.760.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp16.072.000</t>
+          <t>Rp16.969.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>128</v>
       </c>
       <c r="D42" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.691.000</t>
+          <t>Rp2.990.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.350.000</t>
+          <t>Rp10.500.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp26.580.000</t>
+          <t>Rp27.180.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.270.000</t>
+          <t>Rp11.400.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp349.000</t>
+          <t>Rp499.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp2.845.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp3.050.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.501.500</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp10.250.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.600.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.530.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.042.000</t>
+          <t>Rp3.380.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.230.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.754.000</t>
+          <t>Rp1.924.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.257.000</t>
+          <t>Rp4.851.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.535.000</t>
+          <t>Rp3.435.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.900.000</t>
+          <t>Rp13.650.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.326.500</t>
+          <t>Rp15.464.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.739.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.020.000</t>
+          <t>Rp16.325.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp14.892.000</t>
+          <t>Rp15.390.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1288,16 +1288,16 @@
         <v>36</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.741.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.740.000</t>
+          <t>Rp3.888.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp5.285.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.045.000</t>
+          <t>Rp3.435.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp7.763.000</t>
+          <t>Rp8.261.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.025.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.652.000</t>
+          <t>Rp1.392.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp290.000</t>
+          <t>Rp560.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.326.000</t>
+          <t>Rp3.162.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp741.000</t>
+          <t>Rp970.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.196.000</t>
+          <t>Rp1.846.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>96</v>
       </c>
       <c r="D71" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp8.115.000</t>
+          <t>Rp9.340.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.440.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.958.000</t>
+          <t>Rp18.134.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp7.002.000</t>
+          <t>Rp8.558.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.415.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.294.000</t>
+          <t>Rp5.594.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.688.000</t>
+          <t>Rp5.086.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp14.150.000</t>
+          <t>Rp15.250.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.395.000</t>
+          <t>Rp4.595.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp10.380.000</t>
+          <t>Rp9.660.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>77</v>
       </c>
       <c r="D44" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp925.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.786.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.315.000</t>
+          <t>Rp7.590.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp716.000</t>
+          <t>Rp789.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.940.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp2.272.000</t>
+          <t>Rp2.362.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>92</v>
       </c>
       <c r="D68" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp10.535.000</t>
+          <t>Rp9.835.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp10.650.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.325.000</t>
+          <t>Rp18.095.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp24.350.000</t>
+          <t>Rp25.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.210.000</t>
+          <t>Rp5.395.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6443,16 +6443,16 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp752.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp15.320.000</t>
+          <t>Rp14.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>82</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.700.000</t>
+          <t>Rp11.820.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp237.000</t>
+          <t>Rp306.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.875.000</t>
+          <t>Rp17.475.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.184.000</t>
+          <t>Rp8.309.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.190.000</t>
+          <t>Rp15.910.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.256.000</t>
+          <t>Rp2.632.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.575.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp596.000</t>
+          <t>Rp745.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.350.000</t>
+          <t>Rp18.050.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.690.000</t>
+          <t>Rp6.824.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp899.000</t>
+          <t>Rp1.219.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.058.000</t>
+          <t>Rp5.135.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.525.000</t>
+          <t>Rp19.475.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.760.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>128</v>
       </c>
       <c r="D42" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.990.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.500.000</t>
+          <t>Rp11.675.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp9.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.400.000</t>
+          <t>Rp11.900.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.588.000</t>
+          <t>Rp3.887.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.845.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp8.050.000</t>
+          <t>Rp9.305.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.799.981</t>
+          <t>Rp3.999.980</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.785.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>102</v>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp11.050.000</t>
+          <t>Rp10.700.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp5.880.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.599.977</t>
+          <t>Rp5.599.972</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>45</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>144</v>
       </c>
       <c r="D34" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.860.000</t>
+          <t>Rp4.060.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.035.000</t>
+          <t>Rp2.405.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.240.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9397,16 +9397,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.380.000</t>
+          <t>Rp3.549.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.710.000</t>
+          <t>Rp1.780.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.851.000</t>
+          <t>Rp5.049.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp2.079.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp13.650.000</t>
+          <t>Rp13.900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.970.000</t>
+          <t>Rp3.530.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.834.000</t>
+          <t>Rp5.354.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.709.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.888.000</t>
+          <t>Rp4.036.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.261.000</t>
+          <t>Rp9.457.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>45</v>
       </c>
       <c r="D47" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp894.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp970.000</t>
+          <t>Rp1.210.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.846.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.690.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp9.340.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp2.682.000</t>
+          <t>Rp3.576.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.558.000</t>
+          <t>Rp10.114.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.594.000</t>
+          <t>Rp5.694.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.450.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.595.000</t>
+          <t>Rp5.195.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp8.850.000</t>
+          <t>Rp9.225.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.985.000</t>
+          <t>Rp2.786.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp789.000</t>
+          <t>Rp878.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp10.650.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.320.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.395.000</t>
+          <t>Rp5.945.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6536,16 +6536,16 @@
         <v>64</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp399.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp14.000.000</t>
+          <t>Rp14.050.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.570.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.320.000</t>
+          <t>Rp3.720.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.475.000</t>
+          <t>Rp19.675.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp6.475.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp16.969.000</t>
+          <t>Rp17.567.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7982,16 +7982,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp27.180.000</t>
+          <t>Rp27.680.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.700.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.908.000</t>
+          <t>Rp2.067.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.305.000</t>
+          <t>Rp9.335.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.501.500</t>
+          <t>Rp1.617.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp5.880.000</t>
+          <t>Rp6.090.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.405.000</t>
+          <t>Rp2.590.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-25.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-25.xlsx
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1192,14 +1192,14 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp16.990.000</t>
+          <t>Rp18.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp1.210.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.690.000</t>
+          <t>Rp1.765.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.824.000</t>
+          <t>Rp7.148.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.675.000</t>
+          <t>Rp19.925.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.599.000</t>
+          <t>Rp9.387.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.475.000</t>
+          <t>Rp6.575.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp11.675.000</t>
+          <t>Rp11.850.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.599.972</t>
+          <t>Rp5.799.971</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
